--- a/projects/register-room-update/Appendix_A_Equipment_Rooms.xlsx
+++ b/projects/register-room-update/Appendix_A_Equipment_Rooms.xlsx
@@ -25006,7 +25006,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>RDC_NB_AHU8511</t>
+          <t>RDC_NB_2F_AHU8511</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -25023,7 +25023,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>RDC_NB_AHU8512</t>
+          <t>RDC_NB_2F_AHU8512</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -25040,7 +25040,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>RDC_NB_2F_2F_AHU8513</t>
+          <t>RDC_NB_2F_AHU8513</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
